--- a/artfynd/A 22747-2025 artfynd.xlsx
+++ b/artfynd/A 22747-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1117,6 +1117,112 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126379670</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92562</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nästräsk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>731951</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7325770</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22747-2025 artfynd.xlsx
+++ b/artfynd/A 22747-2025 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>126379670</v>
       </c>
       <c r="B6" t="n">
-        <v>92562</v>
+        <v>92565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
